--- a/output/yearly_surface_area_iteration_46_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_46_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497630476921</v>
+        <v>10.84497635408299</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907184627506</v>
+        <v>37.7890720181078</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.981387851348315</v>
+        <v>7.192283681312134</v>
       </c>
       <c r="C2" t="n">
-        <v>6.798602851909163</v>
+        <v>6.261586857686157</v>
       </c>
       <c r="D2" t="n">
-        <v>30.95941385342317</v>
+        <v>33.92232842484004</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.41267819314893</v>
+        <v>19.3453385121834</v>
       </c>
       <c r="C3" t="n">
-        <v>20.11601046001715</v>
+        <v>26.97351817418111</v>
       </c>
       <c r="D3" t="n">
-        <v>70.53366381161209</v>
+        <v>73.49363313991623</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.57719520130167</v>
+        <v>41.32568786256524</v>
       </c>
       <c r="C4" t="n">
-        <v>64.06885517914685</v>
+        <v>89.33904108645974</v>
       </c>
       <c r="D4" t="n">
-        <v>103.5184231788964</v>
+        <v>82.7024266057513</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.07480241863456</v>
+        <v>49.16101629015904</v>
       </c>
       <c r="C5" t="n">
-        <v>98.7147316620168</v>
+        <v>127.4553957038422</v>
       </c>
       <c r="D5" t="n">
-        <v>80.06152528132739</v>
+        <v>54.38882281527331</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.63279496754524</v>
+        <v>43.51203999992289</v>
       </c>
       <c r="C6" t="n">
-        <v>100.4681330618016</v>
+        <v>106.1436165400524</v>
       </c>
       <c r="D6" t="n">
-        <v>52.40765594810324</v>
+        <v>41.05668899160162</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.02126395879071</v>
+        <v>30.06307819944583</v>
       </c>
       <c r="C7" t="n">
-        <v>88.99150239915636</v>
+        <v>70.36676670189013</v>
       </c>
       <c r="D7" t="n">
-        <v>40.90255460203486</v>
+        <v>38.14777054391831</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.27246819789088</v>
+        <v>16.35591675275186</v>
       </c>
       <c r="C8" t="n">
-        <v>61.58503348740241</v>
+        <v>43.97738841173587</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -881,10 +881,10 @@
         <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>37.49687181600267</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>17.45252893839555</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.687456288791196</v>
+        <v>7.721177223387766</v>
       </c>
       <c r="C21" t="n">
-        <v>94.17133953769215</v>
+        <v>96.51471529234708</v>
       </c>
       <c r="D21" t="n">
-        <v>7.687456288791196</v>
+        <v>8.686324376311237</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.856125055832224</v>
+        <v>8.476409678466961</v>
       </c>
       <c r="C2" t="n">
-        <v>6.235079669671493</v>
+        <v>7.219772617031043</v>
       </c>
       <c r="D2" t="n">
-        <v>26.54154918431252</v>
+        <v>27.74026313119787</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.46529165855076</v>
+        <v>21.64262814012093</v>
       </c>
       <c r="C3" t="n">
-        <v>23.25269437508571</v>
+        <v>25.46162670964103</v>
       </c>
       <c r="D3" t="n">
-        <v>77.24881810866027</v>
+        <v>81.62250413107982</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.02465117025996</v>
+        <v>38.76038111136832</v>
       </c>
       <c r="C4" t="n">
-        <v>56.46227396664256</v>
+        <v>78.06955918941061</v>
       </c>
       <c r="D4" t="n">
-        <v>112.4012764069216</v>
+        <v>97.07324950051611</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.11255079975246</v>
+        <v>55.00241513042756</v>
       </c>
       <c r="C5" t="n">
-        <v>108.1640533153924</v>
+        <v>144.439630987312</v>
       </c>
       <c r="D5" t="n">
-        <v>97.04576056479723</v>
+        <v>69.80226177194822</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.81017250684443</v>
+        <v>54.70200033292804</v>
       </c>
       <c r="C6" t="n">
-        <v>126.1889411653638</v>
+        <v>152.4732724511637</v>
       </c>
       <c r="D6" t="n">
-        <v>63.27560303411543</v>
+        <v>47.49695393146069</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.8426679920758</v>
+        <v>40.18391528252619</v>
       </c>
       <c r="C7" t="n">
-        <v>116.1800233205675</v>
+        <v>109.113403345399</v>
       </c>
       <c r="D7" t="n">
-        <v>46.29234949834984</v>
+        <v>41.32176087174825</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.53387512912779</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="C8" t="n">
-        <v>87.87132826861075</v>
+        <v>67.76022654711485</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.75937400146829</v>
+        <v>11.98124898262807</v>
       </c>
       <c r="C9" t="n">
-        <v>56.13437023342411</v>
+        <v>42.82187136383736</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1206,7 +1206,7 @@
         <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>37.01188845010476</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
         <v>35.44600086183109</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>17.45252893839555</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.86996787080585</v>
+        <v>7.905457470880503</v>
       </c>
       <c r="C21" t="n">
-        <v>103.2933283043268</v>
+        <v>105.7354936730267</v>
       </c>
       <c r="D21" t="n">
-        <v>8.853713854656581</v>
+        <v>9.881821838600629</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.394523708386976</v>
+        <v>9.805696070017142</v>
       </c>
       <c r="C2" t="n">
-        <v>12.46819584393449</v>
+        <v>13.60702318086079</v>
       </c>
       <c r="D2" t="n">
-        <v>35.98596209916683</v>
+        <v>40.859357703048</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.21141991377833</v>
+        <v>24.65168485363741</v>
       </c>
       <c r="C3" t="n">
-        <v>23.52267499375358</v>
+        <v>26.48264432205771</v>
       </c>
       <c r="D3" t="n">
-        <v>79.27612711792995</v>
+        <v>83.57127332400974</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.95709050511617</v>
+        <v>39.01563551447249</v>
       </c>
       <c r="C4" t="n">
-        <v>56.50056212710818</v>
+        <v>70.45021525675112</v>
       </c>
       <c r="D4" t="n">
-        <v>122.5604016504676</v>
+        <v>111.8014285596268</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.84886157793756</v>
+        <v>56.00870652728054</v>
       </c>
       <c r="C5" t="n">
-        <v>105.0470043544087</v>
+        <v>143.8751260573701</v>
       </c>
       <c r="D5" t="n">
-        <v>110.2993545721292</v>
+        <v>83.81671025007145</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.65924540229769</v>
+        <v>62.83283481950012</v>
       </c>
       <c r="C6" t="n">
-        <v>146.6367823494164</v>
+        <v>184.4330872152143</v>
       </c>
       <c r="D6" t="n">
-        <v>76.23663622558183</v>
+        <v>56.51332484726341</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.30475236560656</v>
+        <v>50.783845245279</v>
       </c>
       <c r="C7" t="n">
-        <v>144.4465032212417</v>
+        <v>156.4238252130528</v>
       </c>
       <c r="D7" t="n">
-        <v>51.92169083450106</v>
+        <v>44.49575119957818</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.21252483466959</v>
+        <v>32.62838495064274</v>
       </c>
       <c r="C8" t="n">
-        <v>117.4955652442582</v>
+        <v>101.5568912658113</v>
       </c>
       <c r="D8" t="n">
-        <v>41.64082887562846</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.08437354930299</v>
+        <v>16.9734360587231</v>
       </c>
       <c r="C9" t="n">
-        <v>78.65468082114168</v>
+        <v>60.34999487545991</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>49.53898915629405</v>
+        <v>41.56719779780995</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>37.31623023842126</v>
+        <v>36.07235589714055</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
       <c r="D13" t="n">
         <v>33.30088212805181</v>
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>17.45252893839555</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.038111868142588</v>
+        <v>8.073595369415466</v>
       </c>
       <c r="C21" t="n">
-        <v>111.5288021704784</v>
+        <v>114.0395345929935</v>
       </c>
       <c r="D21" t="n">
-        <v>10.04763983517824</v>
+        <v>11.10119363294627</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.700428081484481</v>
+        <v>8.905433425222817</v>
       </c>
       <c r="C2" t="n">
-        <v>8.37823490804228</v>
+        <v>9.251990364821941</v>
       </c>
       <c r="D2" t="n">
-        <v>29.39745325596649</v>
+        <v>33.32837106377072</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.09070600388498</v>
+        <v>28.53449702393355</v>
       </c>
       <c r="C3" t="n">
-        <v>39.31899555508476</v>
+        <v>44.51244091055038</v>
       </c>
       <c r="D3" t="n">
-        <v>87.08593010521332</v>
+        <v>90.2275227588031</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.8700337546077</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="C4" t="n">
-        <v>83.88935958018571</v>
+        <v>111.0484280704695</v>
       </c>
       <c r="D4" t="n">
-        <v>120.2758747426852</v>
+        <v>103.0972534137745</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.16482010778901</v>
+        <v>35.39200473809752</v>
       </c>
       <c r="C5" t="n">
-        <v>87.62098260402784</v>
+        <v>110.2011798017045</v>
       </c>
       <c r="D5" t="n">
-        <v>76.25725292737101</v>
+        <v>56.27868714594842</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.23528495831652</v>
+        <v>31.51704654943536</v>
       </c>
       <c r="C6" t="n">
-        <v>95.11466283054375</v>
+        <v>103.0039873818711</v>
       </c>
       <c r="D6" t="n">
-        <v>34.17365583712723</v>
+        <v>29.3032054763588</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.97838585497334</v>
+        <v>21.61906619521901</v>
       </c>
       <c r="C7" t="n">
-        <v>82.58363513353744</v>
+        <v>71.38483907119408</v>
       </c>
       <c r="D7" t="n">
-        <v>29.2845522699781</v>
+        <v>28.44613973055133</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.849694790259</v>
+        <v>11.76624623539802</v>
       </c>
       <c r="C8" t="n">
-        <v>57.91329707351935</v>
+        <v>44.47807974090174</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>37.82968428774233</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>28.18597658892593</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
         <v>27.12078032981814</v>
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.98146996680633</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.218569885148544</v>
+        <v>5.168901662859456</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4626241528785</v>
+        <v>4.002585390214246</v>
       </c>
       <c r="D2" t="n">
-        <v>20.51852701875834</v>
+        <v>23.12899416435061</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.77302065833651</v>
+        <v>30.40472640052371</v>
       </c>
       <c r="C3" t="n">
-        <v>36.6731854921396</v>
+        <v>41.03705403751668</v>
       </c>
       <c r="D3" t="n">
-        <v>90.21279654323941</v>
+        <v>95.42096811426875</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.20409001595887</v>
+        <v>39.30917807804229</v>
       </c>
       <c r="C4" t="n">
-        <v>93.1806198531775</v>
+        <v>115.1963121209122</v>
       </c>
       <c r="D4" t="n">
-        <v>135.2210200444344</v>
+        <v>122.1392318853457</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.16544200259476</v>
+        <v>39.1226460142354</v>
       </c>
       <c r="C5" t="n">
-        <v>121.1231230114503</v>
+        <v>155.8524480491812</v>
       </c>
       <c r="D5" t="n">
-        <v>94.73865345981721</v>
+        <v>73.36109719984292</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.59504658642736</v>
+        <v>38.07806645691679</v>
       </c>
       <c r="C6" t="n">
-        <v>118.1386099905399</v>
+        <v>135.1248087694183</v>
       </c>
       <c r="D6" t="n">
-        <v>43.47178834404877</v>
+        <v>35.82397372796611</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.66088043587412</v>
+        <v>20.30156077611979</v>
       </c>
       <c r="C7" t="n">
-        <v>105.1608870881013</v>
+        <v>100.0705252415816</v>
       </c>
       <c r="D7" t="n">
-        <v>32.15910954801276</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>76.68922191723958</v>
+        <v>59.99951094504382</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>43.70937128847648</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
+        <v>30.03068052520567</v>
+      </c>
+      <c r="D11" t="n">
         <v>29.852984190737</v>
-      </c>
-      <c r="D11" t="n">
-        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.74995743505333</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.182245220091412</v>
+        <v>4.939172700065703</v>
       </c>
       <c r="C2" t="n">
-        <v>6.450082416901544</v>
+        <v>4.810563750809371</v>
       </c>
       <c r="D2" t="n">
-        <v>21.61219396128928</v>
+        <v>20.43998720241859</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.00172681569702</v>
+        <v>23.91046533693107</v>
       </c>
       <c r="C3" t="n">
-        <v>24.23935081785375</v>
+        <v>27.62638039750524</v>
       </c>
       <c r="D3" t="n">
-        <v>86.65396111534471</v>
+        <v>92.68189201942013</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.88350048502667</v>
+        <v>48.71530283243098</v>
       </c>
       <c r="C4" t="n">
-        <v>92.32551760277855</v>
+        <v>108.636273961135</v>
       </c>
       <c r="D4" t="n">
-        <v>146.0182812957408</v>
+        <v>138.9732597700657</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.42408361716817</v>
+        <v>48.25289966373074</v>
       </c>
       <c r="C5" t="n">
-        <v>147.6303110261141</v>
+        <v>183.4886459237289</v>
       </c>
       <c r="D5" t="n">
-        <v>118.8160159064703</v>
+        <v>95.91675070491338</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.07556318216056</v>
+        <v>44.88059629964295</v>
       </c>
       <c r="C6" t="n">
-        <v>153.278305568646</v>
+        <v>189.4645441994792</v>
       </c>
       <c r="D6" t="n">
-        <v>60.0554705641859</v>
+        <v>47.49695393146069</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.60205768907732</v>
+        <v>30.54217107911827</v>
       </c>
       <c r="C7" t="n">
-        <v>137.260110026155</v>
+        <v>144.5063898312007</v>
       </c>
       <c r="D7" t="n">
-        <v>36.89015173477814</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.52004854581032</v>
+        <v>14.35315143608837</v>
       </c>
       <c r="C8" t="n">
-        <v>106.1465617831651</v>
+        <v>92.46099878596459</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>66.34061936677394</v>
+        <v>53.36093296892687</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>37.5813021185679</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2467,7 +2467,7 @@
         <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
         <v>29.07347651356504</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>19.66637001147211</v>
@@ -2537,7 +2537,7 @@
         <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2579,7 +2579,7 @@
         <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.479894700927443</v>
+        <v>2.952115346670159</v>
       </c>
       <c r="C2" t="n">
-        <v>2.977640786980576</v>
+        <v>2.266855449105885</v>
       </c>
       <c r="D2" t="n">
-        <v>14.9117658798048</v>
+        <v>14.2490861794382</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.93791321492097</v>
+        <v>23.24778563656447</v>
       </c>
       <c r="C3" t="n">
-        <v>26.21757244191107</v>
+        <v>25.58434517267188</v>
       </c>
       <c r="D3" t="n">
-        <v>86.9681203807037</v>
+        <v>91.59215206770618</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.91652005407257</v>
+        <v>53.55237377125501</v>
       </c>
       <c r="C4" t="n">
-        <v>89.415617407391</v>
+        <v>104.7819324742621</v>
       </c>
       <c r="D4" t="n">
-        <v>156.7900171067369</v>
+        <v>150.7021995927024</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.90299657039137</v>
+        <v>49.82369599052564</v>
       </c>
       <c r="C5" t="n">
-        <v>176.9845673830938</v>
+        <v>215.3463589265379</v>
       </c>
       <c r="D5" t="n">
-        <v>127.6517452446915</v>
+        <v>101.9544990860313</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.31328499530853</v>
+        <v>37.19253002768617</v>
       </c>
       <c r="C6" t="n">
-        <v>185.5601335796897</v>
+        <v>224.16147156297</v>
       </c>
       <c r="D6" t="n">
-        <v>58.20389439397641</v>
+        <v>46.93343074922303</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>142.2306986527566</v>
+        <v>141.1527396734936</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>33.95570784678443</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>82.11337798320321</v>
+        <v>67.34298377280996</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>28.6218725696115</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2764,7 +2764,7 @@
         <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.77302065833652</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
         <v>23.27821981539612</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -2834,7 +2834,7 @@
         <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2876,7 +2876,7 @@
         <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.040472640052371</v>
+        <v>3.608904560811275</v>
       </c>
       <c r="C2" t="n">
-        <v>4.176354733865931</v>
+        <v>2.186352137357647</v>
       </c>
       <c r="D2" t="n">
-        <v>16.0525567121396</v>
+        <v>14.29817356465055</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.84264262988003</v>
+        <v>16.92042168269378</v>
       </c>
       <c r="C3" t="n">
-        <v>18.65811511921063</v>
+        <v>17.05786636128833</v>
       </c>
       <c r="D3" t="n">
-        <v>79.43320675060943</v>
+        <v>83.54672963140357</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.72584001527044</v>
+        <v>49.27686251926016</v>
       </c>
       <c r="C4" t="n">
-        <v>78.20994911111789</v>
+        <v>85.59956408098364</v>
       </c>
       <c r="D4" t="n">
-        <v>163.3372925463588</v>
+        <v>159.5467646602619</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.37057051952011</v>
+        <v>62.88094045700822</v>
       </c>
       <c r="C5" t="n">
-        <v>171.0204500797944</v>
+        <v>204.7434837206723</v>
       </c>
       <c r="D5" t="n">
-        <v>151.6800203061322</v>
+        <v>125.8845993770473</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.53720558733482</v>
+        <v>49.22777513404782</v>
       </c>
       <c r="C6" t="n">
-        <v>232.6545709524092</v>
+        <v>280.9565580013522</v>
       </c>
       <c r="D6" t="n">
-        <v>77.72594749292425</v>
+        <v>62.47056991663305</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.25974653546468</v>
+        <v>20.66088043587412</v>
       </c>
       <c r="C7" t="n">
-        <v>197.3263798150876</v>
+        <v>217.8674870310437</v>
       </c>
       <c r="D7" t="n">
-        <v>42.87881273068369</v>
+        <v>38.50709020367265</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>127.6762889372977</v>
+        <v>115.4927999275948</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>56.91093266748334</v>
+        <v>49.14530832689106</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3145,7 +3145,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.3237968159522</v>
+        <v>2.635992585902686</v>
       </c>
       <c r="C2" t="n">
-        <v>2.069524160552276</v>
+        <v>1.888882582970863</v>
       </c>
       <c r="D2" t="n">
-        <v>12.56538886665493</v>
+        <v>10.47033926579223</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.5123744906256</v>
+        <v>15.14345833800705</v>
       </c>
       <c r="C3" t="n">
-        <v>17.89235190989812</v>
+        <v>13.34195130071415</v>
       </c>
       <c r="D3" t="n">
-        <v>75.2067828838269</v>
+        <v>77.55315989697679</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.22059980048183</v>
+        <v>43.98033365484861</v>
       </c>
       <c r="C4" t="n">
-        <v>66.57034832956771</v>
+        <v>69.64616388697297</v>
       </c>
       <c r="D4" t="n">
-        <v>165.7366839355381</v>
+        <v>165.5069549727443</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.8375225738431</v>
+        <v>68.30509652297184</v>
       </c>
       <c r="C5" t="n">
-        <v>164.8599832356456</v>
+        <v>192.1034820284947</v>
       </c>
       <c r="D5" t="n">
-        <v>168.6887992822082</v>
+        <v>142.3534171157875</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.30577517103983</v>
+        <v>58.88817254383644</v>
       </c>
       <c r="C6" t="n">
-        <v>257.570345938489</v>
+        <v>309.6157369837251</v>
       </c>
       <c r="D6" t="n">
-        <v>93.06182838096366</v>
+        <v>75.99512629033711</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.94224111636546</v>
+        <v>18.62473569726624</v>
       </c>
       <c r="C7" t="n">
-        <v>248.6492045499982</v>
+        <v>281.7066132473968</v>
       </c>
       <c r="D7" t="n">
-        <v>48.86747372658923</v>
+        <v>42.57937968088841</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>166.3129698379309</v>
+        <v>158.051562906694</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>66.78436932909349</v>
+        <v>56.79999517690344</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3442,7 +3442,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.843542262126263</v>
+        <v>4.499349728563132</v>
       </c>
       <c r="C2" t="n">
-        <v>7.080364443027996</v>
+        <v>5.229770020522759</v>
       </c>
       <c r="D2" t="n">
-        <v>20.66677092209961</v>
+        <v>21.90770002026757</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.25926350937917</v>
+        <v>12.15403657857551</v>
       </c>
       <c r="C3" t="n">
-        <v>13.17014545247096</v>
+        <v>10.4948829583984</v>
       </c>
       <c r="D3" t="n">
-        <v>68.90396262256239</v>
+        <v>69.56173358440775</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.33698580893068</v>
+        <v>37.17780381212246</v>
       </c>
       <c r="C4" t="n">
-        <v>56.5133248472634</v>
+        <v>53.42474656970293</v>
       </c>
       <c r="D4" t="n">
-        <v>164.9836834463807</v>
+        <v>165.672870334762</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.75130870231863</v>
+        <v>67.32334881872504</v>
       </c>
       <c r="C5" t="n">
-        <v>146.2067768549562</v>
+        <v>164.6390900021901</v>
       </c>
       <c r="D5" t="n">
-        <v>182.0896554451772</v>
+        <v>161.6693031968435</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.28818582782139</v>
+        <v>71.24543089719104</v>
       </c>
       <c r="C6" t="n">
-        <v>260.3879618496773</v>
+        <v>309.0924654573616</v>
       </c>
       <c r="D6" t="n">
-        <v>116.4882920997011</v>
+        <v>94.67189461592844</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.63253292563798</v>
+        <v>35.57264631567892</v>
       </c>
       <c r="C7" t="n">
-        <v>302.3674936832709</v>
+        <v>350.9355343600648</v>
       </c>
       <c r="D7" t="n">
-        <v>59.76683673913732</v>
+        <v>50.42452558552467</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>229.7338715322749</v>
+        <v>238.4125212378167</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>118.8140524110617</v>
+        <v>106.8328034284336</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>33.61405964570653</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>48.82722207071512</v>
+        <v>43.70249905454677</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.87748682561417</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
         <v>20.61179305066178</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3753,7 +3753,7 @@
         <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.115306449753382</v>
+        <v>5.670574739729576</v>
       </c>
       <c r="C2" t="n">
-        <v>5.321072557017713</v>
+        <v>3.669772918474577</v>
       </c>
       <c r="D2" t="n">
-        <v>14.15778364294325</v>
+        <v>4.069344234103029</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.749875319595316</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C2" t="n">
-        <v>4.021238596594936</v>
+        <v>3.012001956629214</v>
       </c>
       <c r="D2" t="n">
-        <v>15.21021718189583</v>
+        <v>16.29897538590555</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.10771451002667</v>
+        <v>16.78297700409922</v>
       </c>
       <c r="C3" t="n">
-        <v>19.46314823669302</v>
+        <v>14.92256510455152</v>
       </c>
       <c r="D3" t="n">
-        <v>77.02301613668351</v>
+        <v>77.1948219849267</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.18904500522568</v>
+        <v>51.33166046424873</v>
       </c>
       <c r="C4" t="n">
-        <v>81.22195106774711</v>
+        <v>81.01774754526377</v>
       </c>
       <c r="D4" t="n">
-        <v>169.1060420565131</v>
+        <v>168.0850244440964</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.36179154344412</v>
+        <v>41.38066573400307</v>
       </c>
       <c r="C5" t="n">
-        <v>218.3652331170968</v>
+        <v>255.4998400302325</v>
       </c>
       <c r="D5" t="n">
-        <v>167.6334205001429</v>
+        <v>144.6850679133737</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.09815907489146</v>
+        <v>22.05790741901734</v>
       </c>
       <c r="C6" t="n">
-        <v>252.7401472335947</v>
+        <v>288.6848759291831</v>
       </c>
       <c r="D6" t="n">
-        <v>91.29075552250242</v>
+        <v>75.27059648460298</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.767186925373263</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>161.5141870595725</v>
+        <v>167.6226212753962</v>
       </c>
       <c r="D7" t="n">
-        <v>34.6743471662931</v>
+        <v>32.15910954801276</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>1.835868206941535</v>
       </c>
       <c r="C8" t="n">
-        <v>87.53753404916685</v>
+        <v>78.69198723390308</v>
       </c>
       <c r="D8" t="n">
-        <v>25.36836067773758</v>
+        <v>24.70077223884975</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>37.27499683484289</v>
+        <v>33.28124717396686</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>22.06477965294707</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="D11" t="n">
         <v>16.52575910558656</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4361,7 +4361,7 @@
         <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.53116656572653</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.081346190732242</v>
+        <v>6.600289815651307</v>
       </c>
       <c r="C2" t="n">
-        <v>5.706899404786709</v>
+        <v>2.790126975469435</v>
       </c>
       <c r="D2" t="n">
-        <v>24.88141381643116</v>
+        <v>11.72206758870692</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.9885221271853</v>
+        <v>12.04604433110836</v>
       </c>
       <c r="C3" t="n">
-        <v>13.4057649014902</v>
+        <v>9.390416791120741</v>
       </c>
       <c r="D3" t="n">
-        <v>15.03055735201867</v>
+        <v>6.715154297048183</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39760830567558</v>
+        <v>13.39970329464181</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14041995324271</v>
+        <v>70.15138783665419</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576189212432421</v>
+        <v>1.576435681722566</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.005931543954486</v>
+        <v>4.39822971502571</v>
       </c>
       <c r="C2" t="n">
-        <v>4.575926049494383</v>
+        <v>2.614394136409256</v>
       </c>
       <c r="D2" t="n">
-        <v>26.21855418961531</v>
+        <v>12.90212832921158</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.86566479543421</v>
+        <v>18.75628988963531</v>
       </c>
       <c r="C3" t="n">
-        <v>18.94282195344221</v>
+        <v>10.34271206424015</v>
       </c>
       <c r="D3" t="n">
-        <v>32.29949946972006</v>
+        <v>14.93729132011522</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.11106066376691</v>
+        <v>14.02622945057418</v>
       </c>
       <c r="C4" t="n">
-        <v>20.99467465531804</v>
+        <v>15.08553522345649</v>
       </c>
       <c r="D4" t="n">
-        <v>22.94737083906494</v>
+        <v>18.58252054598363</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43874909099985</v>
+        <v>15.44683684728715</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13196861294655</v>
+        <v>86.17708977960201</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250262966526285</v>
+        <v>3.251965652060453</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.206208075620835</v>
+        <v>4.434554380082843</v>
       </c>
       <c r="C2" t="n">
-        <v>4.036946559862884</v>
+        <v>9.140071126537803</v>
       </c>
       <c r="D2" t="n">
-        <v>22.37108493667207</v>
+        <v>19.03314274223291</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.44213062427633</v>
+        <v>16.78297700409922</v>
       </c>
       <c r="C3" t="n">
-        <v>18.25068982194821</v>
+        <v>10.24453729381547</v>
       </c>
       <c r="D3" t="n">
-        <v>45.77889544902877</v>
+        <v>21.78989029575796</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.38428962518378</v>
+        <v>26.98039040811084</v>
       </c>
       <c r="C4" t="n">
-        <v>36.55243052451725</v>
+        <v>21.56899706230242</v>
       </c>
       <c r="D4" t="n">
-        <v>33.96159833300992</v>
+        <v>21.72214970416493</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.15541923690726</v>
+        <v>12.51728322914684</v>
       </c>
       <c r="C5" t="n">
-        <v>24.44551783574558</v>
+        <v>18.43231314723387</v>
       </c>
       <c r="D5" t="n">
-        <v>30.90050899116836</v>
+        <v>29.47697482001049</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.82369599052563</v>
       </c>
     </row>
     <row r="11">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>30.17892442854696</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73014982242909</v>
+        <v>16.74938086956505</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0539139168175</v>
+        <v>102.1712233043468</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182537455607273</v>
+        <v>5.024814260869515</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.142394474844792</v>
+        <v>7.316965639751478</v>
       </c>
       <c r="C2" t="n">
-        <v>7.9256492163845</v>
+        <v>9.634871969478198</v>
       </c>
       <c r="D2" t="n">
-        <v>28.34501971701391</v>
+        <v>21.8370141855618</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.11324514335365</v>
+        <v>15.94849145548944</v>
       </c>
       <c r="C3" t="n">
-        <v>16.74861583445059</v>
+        <v>25.06401888942107</v>
       </c>
       <c r="D3" t="n">
-        <v>52.59713325502287</v>
+        <v>31.40610905885546</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.49388551516093</v>
+        <v>30.24764676784423</v>
       </c>
       <c r="C4" t="n">
-        <v>41.64475586644545</v>
+        <v>23.67484588791183</v>
       </c>
       <c r="D4" t="n">
-        <v>48.43452298901639</v>
+        <v>27.22288209105981</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.7343726449724</v>
+        <v>26.67899386290708</v>
       </c>
       <c r="C5" t="n">
-        <v>47.46750150033328</v>
+        <v>30.43417883165113</v>
       </c>
       <c r="D5" t="n">
-        <v>35.58835427894688</v>
+        <v>30.80233422074368</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.95474179461341</v>
+        <v>11.63272854762046</v>
       </c>
       <c r="C6" t="n">
-        <v>26.24407962992574</v>
+        <v>21.37362926915731</v>
       </c>
       <c r="D6" t="n">
-        <v>38.48058301565798</v>
+        <v>37.75605320992383</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>20.84054026575129</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>41.71249645803847</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.56104526967722</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>46.09305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>37.91411459030757</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05512576856882</v>
+        <v>18.08891517977551</v>
       </c>
       <c r="C21" t="n">
-        <v>117.788201442568</v>
+        <v>118.0086371252021</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018375256189607</v>
+        <v>6.891015306581147</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.647814616082654</v>
+        <v>6.616979526623502</v>
       </c>
       <c r="C2" t="n">
-        <v>8.580474935117122</v>
+        <v>11.54731649735098</v>
       </c>
       <c r="D2" t="n">
-        <v>24.96584411899639</v>
+        <v>30.86418432611122</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.86504290062846</v>
+        <v>19.24225500323749</v>
       </c>
       <c r="C3" t="n">
-        <v>23.29687302177681</v>
+        <v>30.53726234059704</v>
       </c>
       <c r="D3" t="n">
-        <v>58.7428738836079</v>
+        <v>39.45153149515808</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.54271085846601</v>
+        <v>22.24542123052848</v>
       </c>
       <c r="C4" t="n">
-        <v>34.95709050511617</v>
+        <v>38.88800831292041</v>
       </c>
       <c r="D4" t="n">
-        <v>55.020086589104</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.63557597974196</v>
+        <v>22.31021657900877</v>
       </c>
       <c r="C5" t="n">
-        <v>46.68210333693584</v>
+        <v>28.17615911188346</v>
       </c>
       <c r="D5" t="n">
-        <v>35.71107274197773</v>
+        <v>27.39076094848602</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.44405306195583</v>
+        <v>13.4038014060817</v>
       </c>
       <c r="C6" t="n">
-        <v>35.17994723398021</v>
+        <v>24.15099352447154</v>
       </c>
       <c r="D6" t="n">
-        <v>31.83905979642831</v>
+        <v>30.10823859384119</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>18.98405535702057</v>
+        <v>16.88802400845363</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.91876128692155</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.056556326943641</v>
+        <v>7.075763994650552</v>
       </c>
       <c r="C21" t="n">
-        <v>66.15521556509663</v>
+        <v>67.21975794918023</v>
       </c>
       <c r="D21" t="n">
-        <v>4.410347704339776</v>
+        <v>5.306822995987914</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.912084674974292</v>
+        <v>6.861434704980958</v>
       </c>
       <c r="C2" t="n">
-        <v>5.696100180039994</v>
+        <v>8.886780218842128</v>
       </c>
       <c r="D2" t="n">
-        <v>25.10917928381642</v>
+        <v>32.33778763018569</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.56547098211294</v>
+        <v>21.83406894244906</v>
       </c>
       <c r="C3" t="n">
-        <v>30.23782929080176</v>
+        <v>40.28110830524663</v>
       </c>
       <c r="D3" t="n">
-        <v>65.52184178143213</v>
+        <v>56.70083865877454</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.8692729910817</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="C4" t="n">
-        <v>49.37896428050182</v>
+        <v>63.35414285045516</v>
       </c>
       <c r="D4" t="n">
-        <v>72.51777592189489</v>
+        <v>45.51186007347363</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.41592653589794</v>
+        <v>29.03518835309942</v>
       </c>
       <c r="C5" t="n">
-        <v>57.92311455056183</v>
+        <v>55.76326960121884</v>
       </c>
       <c r="D5" t="n">
-        <v>48.74377351585415</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.35225180384214</v>
+        <v>23.54721868635975</v>
       </c>
       <c r="C6" t="n">
-        <v>58.56615929684348</v>
+        <v>36.74976181307086</v>
       </c>
       <c r="D6" t="n">
-        <v>36.18623863083319</v>
+        <v>32.6440929139107</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.67788894201581</v>
+        <v>11.73777555197486</v>
       </c>
       <c r="C7" t="n">
-        <v>37.90822410408209</v>
+        <v>27.84727363096077</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>22.86490403190821</v>
+        <v>21.27938148954961</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.5935407549086</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.279403509217063</v>
+        <v>7.304663797702396</v>
       </c>
       <c r="C21" t="n">
-        <v>75.52381140812703</v>
+        <v>77.61205285058796</v>
       </c>
       <c r="D21" t="n">
-        <v>5.459552631912797</v>
+        <v>6.391580822989597</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.659374604355362</v>
+        <v>4.759512870188536</v>
       </c>
       <c r="C2" t="n">
-        <v>4.16751900452771</v>
+        <v>5.105088062083413</v>
       </c>
       <c r="D2" t="n">
-        <v>20.77279967415826</v>
+        <v>25.68644693391354</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.392282475538</v>
+        <v>23.0219836645877</v>
       </c>
       <c r="C3" t="n">
-        <v>25.34381698513141</v>
+        <v>36.79590395517045</v>
       </c>
       <c r="D3" t="n">
-        <v>70.40603661006001</v>
+        <v>69.41447142877074</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.27990557336413</v>
+        <v>38.1350078237631</v>
       </c>
       <c r="C4" t="n">
-        <v>64.91119470939061</v>
+        <v>85.86758120424302</v>
       </c>
       <c r="D4" t="n">
-        <v>89.09654940351078</v>
+        <v>63.2520410892135</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.36179154344412</v>
+        <v>39.98167525545136</v>
       </c>
       <c r="C5" t="n">
-        <v>76.40451508300804</v>
+        <v>90.83620633543615</v>
       </c>
       <c r="D5" t="n">
-        <v>63.32272692391928</v>
+        <v>42.41150082346221</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.25415914887547</v>
+        <v>32.6440929139107</v>
       </c>
       <c r="C6" t="n">
-        <v>77.4441859018054</v>
+        <v>66.21397391292614</v>
       </c>
       <c r="D6" t="n">
-        <v>43.63279496754524</v>
+        <v>35.74347041621788</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.19985992550562</v>
+        <v>20.60099382591507</v>
       </c>
       <c r="C7" t="n">
-        <v>63.89901282631214</v>
+        <v>42.27994663109313</v>
       </c>
       <c r="D7" t="n">
-        <v>36.59071868498287</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>38.05254101660637</v>
+        <v>30.29182541453534</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>26.5140602485936</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>22.12466626290612</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>17.45252893839555</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.490023576464325</v>
+        <v>7.520227116337329</v>
       </c>
       <c r="C21" t="n">
-        <v>85.19901818228169</v>
+        <v>87.42264022742145</v>
       </c>
       <c r="D21" t="n">
-        <v>6.553770629406285</v>
+        <v>7.520227116337329</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_46_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_46_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497635408299</v>
+        <v>10.84497622452601</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890720181078</v>
+        <v>37.78907156666948</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.192283681312134</v>
+        <v>5.345616249623882</v>
       </c>
       <c r="C2" t="n">
-        <v>6.261586857686157</v>
+        <v>9.926451037639499</v>
       </c>
       <c r="D2" t="n">
-        <v>33.92232842484004</v>
+        <v>24.91872022919254</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.3453385121834</v>
+        <v>17.81381209355838</v>
       </c>
       <c r="C3" t="n">
-        <v>26.97351817418111</v>
+        <v>48.7094123462055</v>
       </c>
       <c r="D3" t="n">
-        <v>73.49363313991623</v>
+        <v>67.14663423196059</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.32568786256524</v>
+        <v>33.92331017254428</v>
       </c>
       <c r="C4" t="n">
-        <v>89.33904108645974</v>
+        <v>91.87882239734626</v>
       </c>
       <c r="D4" t="n">
-        <v>82.7024266057513</v>
+        <v>89.55600732909829</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.16101629015904</v>
+        <v>43.09872421643498</v>
       </c>
       <c r="C5" t="n">
-        <v>127.4553957038422</v>
+        <v>133.7876683962341</v>
       </c>
       <c r="D5" t="n">
-        <v>54.38882281527331</v>
+        <v>65.16350386938205</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.51203999992289</v>
+        <v>40.57366912111219</v>
       </c>
       <c r="C6" t="n">
-        <v>106.1436165400524</v>
+        <v>138.9084644215855</v>
       </c>
       <c r="D6" t="n">
-        <v>41.05668899160162</v>
+        <v>45.00135126726531</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.06307819944583</v>
+        <v>27.42806736124739</v>
       </c>
       <c r="C7" t="n">
-        <v>70.36676670189013</v>
+        <v>118.815034158766</v>
       </c>
       <c r="D7" t="n">
-        <v>38.14777054391831</v>
+        <v>38.20765715387736</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.35591675275186</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>43.97738841173587</v>
+        <v>75.68783925890784</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>32.06093477758807</v>
+        <v>40.93593402397924</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.27567548291088</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.721177223387766</v>
+        <v>7.676974062771676</v>
       </c>
       <c r="C21" t="n">
-        <v>96.51471529234708</v>
+        <v>95.0025540267995</v>
       </c>
       <c r="D21" t="n">
-        <v>8.686324376311237</v>
+        <v>8.636595820618137</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.476409678466961</v>
+        <v>6.753442457513809</v>
       </c>
       <c r="C2" t="n">
-        <v>7.219772617031043</v>
+        <v>7.650759859195394</v>
       </c>
       <c r="D2" t="n">
-        <v>27.74026313119787</v>
+        <v>31.13809193559609</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.64262814012093</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="C3" t="n">
-        <v>25.46162670964103</v>
+        <v>43.37361357362408</v>
       </c>
       <c r="D3" t="n">
-        <v>81.62250413107982</v>
+        <v>70.09187734470103</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.76038111136832</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="C4" t="n">
-        <v>78.06955918941061</v>
+        <v>105.1010004781423</v>
       </c>
       <c r="D4" t="n">
-        <v>97.07324950051611</v>
+        <v>99.02594568426302</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.00241513042756</v>
+        <v>46.36303533305563</v>
       </c>
       <c r="C5" t="n">
-        <v>144.439630987312</v>
+        <v>150.354660905399</v>
       </c>
       <c r="D5" t="n">
-        <v>69.80226177194822</v>
+        <v>79.61973881441634</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.70200033292804</v>
+        <v>48.7850069194325</v>
       </c>
       <c r="C6" t="n">
-        <v>152.4732724511637</v>
+        <v>170.9890341532585</v>
       </c>
       <c r="D6" t="n">
-        <v>47.49695393146069</v>
+        <v>52.85042416271855</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.18391528252619</v>
+        <v>36.53083207502382</v>
       </c>
       <c r="C7" t="n">
-        <v>109.113403345399</v>
+        <v>155.4656394537079</v>
       </c>
       <c r="D7" t="n">
-        <v>41.32176087174825</v>
+        <v>42.04040019125691</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.94973524510094</v>
+        <v>21.02903582496668</v>
       </c>
       <c r="C8" t="n">
-        <v>67.76022654711485</v>
+        <v>113.4900346109313</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.98124898262807</v>
+        <v>10.31718662392973</v>
       </c>
       <c r="C9" t="n">
-        <v>42.82187136383736</v>
+        <v>64.45468202691582</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>39.00483628972578</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.24313893995049</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
         <v>33.04071898642641</v>
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.905457470880503</v>
+        <v>7.85060197655788</v>
       </c>
       <c r="C21" t="n">
-        <v>105.7354936730267</v>
+        <v>103.0391509423222</v>
       </c>
       <c r="D21" t="n">
-        <v>9.881821838600629</v>
+        <v>9.81325247069735</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.805696070017142</v>
+        <v>7.943320675060943</v>
       </c>
       <c r="C2" t="n">
-        <v>13.60702318086079</v>
+        <v>9.004589943351744</v>
       </c>
       <c r="D2" t="n">
-        <v>40.859357703048</v>
+        <v>32.90229256012761</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.65168485363741</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="C3" t="n">
-        <v>26.48264432205771</v>
+        <v>36.78117773960675</v>
       </c>
       <c r="D3" t="n">
-        <v>83.57127332400974</v>
+        <v>75.87437132271474</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.01563551447249</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="C4" t="n">
-        <v>70.45021525675112</v>
+        <v>106.1475435308694</v>
       </c>
       <c r="D4" t="n">
-        <v>111.8014285596268</v>
+        <v>107.9981379533746</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.00870652728054</v>
+        <v>47.41841411512095</v>
       </c>
       <c r="C5" t="n">
-        <v>143.8751260573701</v>
+        <v>166.6516727958961</v>
       </c>
       <c r="D5" t="n">
-        <v>83.81671025007145</v>
+        <v>91.32708018755955</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.83283481950012</v>
+        <v>54.05797383894213</v>
       </c>
       <c r="C6" t="n">
-        <v>184.4330872152143</v>
+        <v>197.5953786860513</v>
       </c>
       <c r="D6" t="n">
-        <v>56.51332484726341</v>
+        <v>62.59132488425541</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.783845245279</v>
+        <v>45.03473068920969</v>
       </c>
       <c r="C7" t="n">
-        <v>156.4238252130528</v>
+        <v>194.1523894872577</v>
       </c>
       <c r="D7" t="n">
-        <v>44.49575119957818</v>
+        <v>45.8132566186774</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.62838495064274</v>
+        <v>28.45595720759379</v>
       </c>
       <c r="C8" t="n">
-        <v>101.5568912658113</v>
+        <v>150.7080900789279</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.9734360587231</v>
+        <v>14.75468624712531</v>
       </c>
       <c r="C9" t="n">
-        <v>60.34999487545991</v>
+        <v>95.07342942696533</v>
       </c>
       <c r="D9" t="n">
         <v>37.05312185368311</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>41.56719779780995</v>
+        <v>54.37900533823083</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.13853390395258</v>
       </c>
       <c r="D11" t="n">
         <v>36.96083756948391</v>
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.073595369415466</v>
+        <v>8.006806643552572</v>
       </c>
       <c r="C21" t="n">
-        <v>114.0395345929935</v>
+        <v>110.0935913488479</v>
       </c>
       <c r="D21" t="n">
-        <v>11.10119363294627</v>
+        <v>11.00935913488478</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.905433425222817</v>
+        <v>7.252170291271189</v>
       </c>
       <c r="C2" t="n">
-        <v>9.251990364821941</v>
+        <v>6.266495596207391</v>
       </c>
       <c r="D2" t="n">
-        <v>33.32837106377072</v>
+        <v>27.05009449511237</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.53449702393355</v>
+        <v>22.70782439922873</v>
       </c>
       <c r="C3" t="n">
-        <v>44.51244091055038</v>
+        <v>57.62859023928777</v>
       </c>
       <c r="D3" t="n">
-        <v>90.2275227588031</v>
+        <v>81.95629835052374</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.90381408717959</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="C4" t="n">
-        <v>111.0484280704695</v>
+        <v>139.2285141731699</v>
       </c>
       <c r="D4" t="n">
-        <v>103.0972534137745</v>
+        <v>103.3142196564131</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.39200473809752</v>
+        <v>30.43417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>110.2011798017045</v>
+        <v>118.055161435679</v>
       </c>
       <c r="D5" t="n">
-        <v>56.27868714594842</v>
+        <v>61.94828013797375</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.51704654943536</v>
+        <v>27.93464917663875</v>
       </c>
       <c r="C6" t="n">
-        <v>103.0039873818711</v>
+        <v>127.8795107120768</v>
       </c>
       <c r="D6" t="n">
-        <v>29.3032054763588</v>
+        <v>30.14849024971531</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.61906619521901</v>
+        <v>18.86428213710246</v>
       </c>
       <c r="C7" t="n">
-        <v>71.38483907119408</v>
+        <v>105.9394130175691</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>27.72750041104266</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>44.47807974090174</v>
+        <v>70.01333752836128</v>
       </c>
       <c r="D8" t="n">
         <v>27.28767743954009</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>31.72812230584841</v>
+        <v>41.49062147687869</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.18597658892593</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
         <v>28.89774367450487</v>
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
         <v>24.58296251434014</v>
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.98146996680633</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.168901662859456</v>
+        <v>4.282383485924587</v>
       </c>
       <c r="C2" t="n">
-        <v>4.002585390214246</v>
+        <v>3.290818304635308</v>
       </c>
       <c r="D2" t="n">
-        <v>23.12899416435061</v>
+        <v>19.87940926329366</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.40472640052371</v>
+        <v>24.27371198750239</v>
       </c>
       <c r="C3" t="n">
-        <v>41.03705403751668</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D3" t="n">
-        <v>95.42096811426875</v>
+        <v>85.26969685235672</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.30917807804229</v>
+        <v>31.34524070119216</v>
       </c>
       <c r="C4" t="n">
-        <v>115.1963121209122</v>
+        <v>146.4522137810179</v>
       </c>
       <c r="D4" t="n">
-        <v>122.1392318853457</v>
+        <v>116.9703302224862</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.1226460142354</v>
+        <v>33.69848994827177</v>
       </c>
       <c r="C5" t="n">
-        <v>155.8524480491812</v>
+        <v>179.0462375620121</v>
       </c>
       <c r="D5" t="n">
-        <v>73.36109719984292</v>
+        <v>78.9079717288374</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.07806645691679</v>
+        <v>32.72459622565894</v>
       </c>
       <c r="C6" t="n">
-        <v>135.1248087694183</v>
+        <v>157.7864910265474</v>
       </c>
       <c r="D6" t="n">
-        <v>35.82397372796611</v>
+        <v>36.8302651248191</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.30156077611979</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="C7" t="n">
-        <v>100.0705252415816</v>
+        <v>135.6431715572606</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>30.12296480940488</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>59.99951094504382</v>
+        <v>93.12858722485242</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>37.16405934426299</v>
+        <v>45.15155866601504</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.74995743505333</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.939172700065703</v>
+        <v>4.843943172753763</v>
       </c>
       <c r="C2" t="n">
-        <v>4.810563750809371</v>
+        <v>4.437499623195583</v>
       </c>
       <c r="D2" t="n">
-        <v>20.43998720241859</v>
+        <v>27.31320287985051</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.91046533693107</v>
+        <v>19.42878706704438</v>
       </c>
       <c r="C3" t="n">
-        <v>27.62638039750524</v>
+        <v>27.0716929446058</v>
       </c>
       <c r="D3" t="n">
-        <v>92.68189201942013</v>
+        <v>81.4605157598791</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.71530283243098</v>
+        <v>38.32644862609123</v>
       </c>
       <c r="C4" t="n">
-        <v>108.636273961135</v>
+        <v>125.7000308086489</v>
       </c>
       <c r="D4" t="n">
-        <v>138.9732597700657</v>
+        <v>130.4988135870073</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.25289966373074</v>
+        <v>39.5398887885403</v>
       </c>
       <c r="C5" t="n">
-        <v>183.4886459237289</v>
+        <v>221.6050005411113</v>
       </c>
       <c r="D5" t="n">
-        <v>95.91675070491338</v>
+        <v>98.93562489547234</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.88059629964295</v>
+        <v>38.19882142453915</v>
       </c>
       <c r="C6" t="n">
-        <v>189.4645441994792</v>
+        <v>216.5136569468874</v>
       </c>
       <c r="D6" t="n">
-        <v>47.49695393146069</v>
+        <v>49.67054334866313</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.54217107911827</v>
+        <v>25.81112889235289</v>
       </c>
       <c r="C7" t="n">
-        <v>144.5063898312007</v>
+        <v>176.3660663294182</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.35315143608837</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="C8" t="n">
-        <v>92.46099878596459</v>
+        <v>131.5149224609027</v>
       </c>
       <c r="D8" t="n">
-        <v>29.95803119509142</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>53.36093296892687</v>
+        <v>73.99530621678632</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>37.5813021185679</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>30.38607319414302</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>29.07347651356504</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.952115346670159</v>
+        <v>2.921681167838508</v>
       </c>
       <c r="C2" t="n">
-        <v>2.266855449105885</v>
+        <v>2.156899706230242</v>
       </c>
       <c r="D2" t="n">
-        <v>14.2490861794382</v>
+        <v>19.07437614581128</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.24778563656447</v>
+        <v>19.79694245613693</v>
       </c>
       <c r="C3" t="n">
-        <v>25.58434517267188</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D3" t="n">
-        <v>91.59215206770618</v>
+        <v>85.36296288426017</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.55237377125501</v>
+        <v>41.98934931063608</v>
       </c>
       <c r="C4" t="n">
-        <v>104.7819324742621</v>
+        <v>118.1572631969206</v>
       </c>
       <c r="D4" t="n">
-        <v>150.7021995927024</v>
+        <v>140.7983287522605</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.82369599052564</v>
+        <v>40.96342295969817</v>
       </c>
       <c r="C5" t="n">
-        <v>215.3463589265379</v>
+        <v>259.6968114658875</v>
       </c>
       <c r="D5" t="n">
-        <v>101.9544990860313</v>
+        <v>103.8443634167064</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.19253002768617</v>
+        <v>30.83276839957533</v>
       </c>
       <c r="C6" t="n">
-        <v>224.16147156297</v>
+        <v>250.7678160957628</v>
       </c>
       <c r="D6" t="n">
-        <v>46.93343074922303</v>
+        <v>48.26173539306896</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>8.024805734513427</v>
       </c>
       <c r="C7" t="n">
-        <v>141.1527396734936</v>
+        <v>179.7197164871253</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>67.34298377280996</v>
+        <v>91.87685890193774</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>28.6218725696115</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.77302065833652</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
         <v>23.27821981539612</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.608904560811275</v>
+        <v>2.739076094848601</v>
       </c>
       <c r="C2" t="n">
-        <v>2.186352137357647</v>
+        <v>5.023603002630929</v>
       </c>
       <c r="D2" t="n">
-        <v>14.29817356465055</v>
+        <v>17.68814838741478</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.92042168269378</v>
+        <v>15.18272824617692</v>
       </c>
       <c r="C3" t="n">
-        <v>17.05786636128833</v>
+        <v>16.74370709592935</v>
       </c>
       <c r="D3" t="n">
-        <v>83.54672963140357</v>
+        <v>81.04327298557421</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.27686251926016</v>
+        <v>39.83244960440584</v>
       </c>
       <c r="C4" t="n">
-        <v>85.59956408098364</v>
+        <v>91.43212719191393</v>
       </c>
       <c r="D4" t="n">
-        <v>159.5467646602619</v>
+        <v>148.9792323717492</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.88094045700822</v>
+        <v>49.87278337573798</v>
       </c>
       <c r="C5" t="n">
-        <v>204.7434837206723</v>
+        <v>242.7371198750239</v>
       </c>
       <c r="D5" t="n">
-        <v>125.8845993770473</v>
+        <v>124.7065021319511</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.22777513404782</v>
+        <v>39.9698942830004</v>
       </c>
       <c r="C6" t="n">
-        <v>280.9565580013522</v>
+        <v>321.6107304342127</v>
       </c>
       <c r="D6" t="n">
-        <v>62.47056991663305</v>
+        <v>64.48315271033901</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.66088043587412</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="C7" t="n">
-        <v>217.8674870310437</v>
+        <v>257.0333299442659</v>
       </c>
       <c r="D7" t="n">
-        <v>38.50709020367265</v>
+        <v>37.72856427420492</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>115.4927999275948</v>
+        <v>147.9542877685155</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>32.87873061522568</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>49.14530832689106</v>
+        <v>59.68436993198057</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>14.82929907264807</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.86995163914969</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.52062938288707</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.13520344574558</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.635992585902686</v>
+        <v>1.963495408493621</v>
       </c>
       <c r="C2" t="n">
-        <v>1.888882582970863</v>
+        <v>2.919717672430014</v>
       </c>
       <c r="D2" t="n">
-        <v>10.47033926579223</v>
+        <v>14.30210055546753</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.14345833800705</v>
+        <v>12.92470852640926</v>
       </c>
       <c r="C3" t="n">
-        <v>13.34195130071415</v>
+        <v>18.28014225307561</v>
       </c>
       <c r="D3" t="n">
-        <v>77.55315989697679</v>
+        <v>77.59242980514665</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.98033365484861</v>
+        <v>36.22059980048183</v>
       </c>
       <c r="C4" t="n">
-        <v>69.64616388697297</v>
+        <v>73.76852249710534</v>
       </c>
       <c r="D4" t="n">
-        <v>165.5069549727443</v>
+        <v>153.5738116276243</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.30509652297184</v>
+        <v>54.70789081915352</v>
       </c>
       <c r="C5" t="n">
-        <v>192.1034820284947</v>
+        <v>222.1940491636594</v>
       </c>
       <c r="D5" t="n">
-        <v>142.3534171157875</v>
+        <v>140.3899217072939</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.88817254383644</v>
+        <v>46.249152599363</v>
       </c>
       <c r="C6" t="n">
-        <v>309.6157369837251</v>
+        <v>357.3139491945564</v>
       </c>
       <c r="D6" t="n">
-        <v>75.99512629033711</v>
+        <v>75.71336469921827</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.62473569726624</v>
+        <v>14.61233283000952</v>
       </c>
       <c r="C7" t="n">
-        <v>281.7066132473968</v>
+        <v>324.4656527581623</v>
       </c>
       <c r="D7" t="n">
-        <v>42.57937968088841</v>
+        <v>41.98051358129786</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>158.051562906694</v>
+        <v>192.3489189545563</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>56.79999517690344</v>
+        <v>66.22968187619405</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
         <v>25.48126166372597</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>22.38973814305275</v>
+      </c>
+      <c r="D11" t="n">
         <v>24.16670148773948</v>
-      </c>
-      <c r="D11" t="n">
-        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.499349728563132</v>
+        <v>2.835287369864788</v>
       </c>
       <c r="C2" t="n">
-        <v>5.229770020522759</v>
+        <v>17.44762019987432</v>
       </c>
       <c r="D2" t="n">
-        <v>21.90770002026757</v>
+        <v>17.14327841155781</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.15403657857551</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C3" t="n">
-        <v>10.4948829583984</v>
+        <v>15.07964473723101</v>
       </c>
       <c r="D3" t="n">
-        <v>69.56173358440775</v>
+        <v>72.06519023023712</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.17780381212246</v>
+        <v>30.70710469343173</v>
       </c>
       <c r="C4" t="n">
-        <v>53.42474656970293</v>
+        <v>61.64393834965723</v>
       </c>
       <c r="D4" t="n">
-        <v>165.672870334762</v>
+        <v>155.3733551695087</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.32334881872504</v>
+        <v>54.87969666739671</v>
       </c>
       <c r="C5" t="n">
-        <v>164.6390900021901</v>
+        <v>186.7038696551372</v>
       </c>
       <c r="D5" t="n">
-        <v>161.6693031968435</v>
+        <v>154.1098458741431</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>71.24543089719104</v>
+        <v>55.2252718592916</v>
       </c>
       <c r="C6" t="n">
-        <v>309.0924654573616</v>
+        <v>357.0321876034376</v>
       </c>
       <c r="D6" t="n">
-        <v>94.67189461592844</v>
+        <v>94.02786812194252</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.57264631567892</v>
+        <v>27.5478405811655</v>
       </c>
       <c r="C7" t="n">
-        <v>350.9355343600648</v>
+        <v>397.4075436882918</v>
       </c>
       <c r="D7" t="n">
-        <v>50.42452558552467</v>
+        <v>49.82565948593412</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>238.4125212378167</v>
+        <v>280.637489997472</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>106.8328034284336</v>
+        <v>123.6953019965768</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61405964570653</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>43.70249905454677</v>
+        <v>46.26486056263094</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.76244241776806</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.25371718051895</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.670574739729576</v>
+        <v>4.677046063031804</v>
       </c>
       <c r="C2" t="n">
-        <v>3.669772918474577</v>
+        <v>6.48542533425443</v>
       </c>
       <c r="D2" t="n">
-        <v>4.069344234103029</v>
+        <v>6.401976779393451</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.254493639578176</v>
+        <v>2.072469403665017</v>
       </c>
       <c r="C2" t="n">
-        <v>3.012001956629214</v>
+        <v>10.32896759638069</v>
       </c>
       <c r="D2" t="n">
-        <v>16.29897538590555</v>
+        <v>12.75486617357456</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.78297700409922</v>
+        <v>13.57266201121215</v>
       </c>
       <c r="C3" t="n">
-        <v>14.92256510455152</v>
+        <v>31.69081589308704</v>
       </c>
       <c r="D3" t="n">
-        <v>77.1948219849267</v>
+        <v>78.56926877087224</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.33166046424873</v>
+        <v>41.79790850830795</v>
       </c>
       <c r="C4" t="n">
-        <v>81.01774754526377</v>
+        <v>94.21440018574941</v>
       </c>
       <c r="D4" t="n">
-        <v>168.0850244440964</v>
+        <v>156.4581863827015</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.38066573400307</v>
+        <v>31.6122760767473</v>
       </c>
       <c r="C5" t="n">
-        <v>255.4998400302325</v>
+        <v>291.4318060056657</v>
       </c>
       <c r="D5" t="n">
-        <v>144.6850679133737</v>
+        <v>139.6045235438964</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.05790741901734</v>
+        <v>17.10695374650067</v>
       </c>
       <c r="C6" t="n">
-        <v>288.6848759291831</v>
+        <v>324.7101079365199</v>
       </c>
       <c r="D6" t="n">
-        <v>75.27059648460298</v>
+        <v>74.02279515250527</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.347980655659875</v>
+        <v>4.910702016642545</v>
       </c>
       <c r="C7" t="n">
-        <v>167.6226212753962</v>
+        <v>197.3263798150876</v>
       </c>
       <c r="D7" t="n">
-        <v>32.15910954801276</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>78.69198723390308</v>
+        <v>91.12582190818894</v>
       </c>
       <c r="D8" t="n">
-        <v>24.70077223884975</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>33.28124717396686</v>
+        <v>35.27812200440487</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>20.41249826669968</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.06477965294707</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.53116656572653</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.600289815651307</v>
+        <v>7.208973392284329</v>
       </c>
       <c r="C2" t="n">
-        <v>2.790126975469435</v>
+        <v>8.173049637854696</v>
       </c>
       <c r="D2" t="n">
-        <v>11.72206758870692</v>
+        <v>17.45449243380404</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.04604433110836</v>
+        <v>9.940195505498956</v>
       </c>
       <c r="C3" t="n">
-        <v>9.390416791120741</v>
+        <v>16.60135367881356</v>
       </c>
       <c r="D3" t="n">
-        <v>6.715154297048183</v>
+        <v>8.511752595819846</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39970329464181</v>
+        <v>13.39898769373022</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15138783665419</v>
+        <v>70.14764145541113</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576435681722566</v>
+        <v>1.576351493380025</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.39822971502571</v>
+        <v>4.432590884674349</v>
       </c>
       <c r="C2" t="n">
-        <v>2.614394136409256</v>
+        <v>5.667629496616836</v>
       </c>
       <c r="D2" t="n">
-        <v>12.90212832921158</v>
+        <v>15.42816517223863</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.75628988963531</v>
+        <v>18.85446466005999</v>
       </c>
       <c r="C3" t="n">
-        <v>10.34271206424015</v>
+        <v>26.15375884113503</v>
       </c>
       <c r="D3" t="n">
-        <v>14.93729132011522</v>
+        <v>21.11248437982766</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.02622945057418</v>
+        <v>11.65236350170539</v>
       </c>
       <c r="C4" t="n">
-        <v>15.08553522345649</v>
+        <v>25.83174559414208</v>
       </c>
       <c r="D4" t="n">
-        <v>18.58252054598363</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="5">
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
         <v>16.54343056426301</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4910,7 +4910,7 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
         <v>36.80081269369168</v>
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5008,7 +5008,7 @@
         <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>26.87534340375643</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44683684728715</v>
+        <v>15.44241494232473</v>
       </c>
       <c r="C21" t="n">
-        <v>86.17708977960201</v>
+        <v>86.15242020454849</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251965652060453</v>
+        <v>3.251034724699943</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.434554380082843</v>
+        <v>5.058945919983814</v>
       </c>
       <c r="C2" t="n">
-        <v>9.140071126537803</v>
+        <v>8.883834975729387</v>
       </c>
       <c r="D2" t="n">
-        <v>19.03314274223291</v>
+        <v>25.77185898418302</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.78297700409922</v>
+        <v>16.87624303600267</v>
       </c>
       <c r="C3" t="n">
-        <v>10.24453729381547</v>
+        <v>23.66502841086936</v>
       </c>
       <c r="D3" t="n">
-        <v>21.78989029575796</v>
+        <v>28.55413197801848</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.98039040811084</v>
+        <v>25.62754207165874</v>
       </c>
       <c r="C4" t="n">
-        <v>21.56899706230242</v>
+        <v>49.17476075801849</v>
       </c>
       <c r="D4" t="n">
-        <v>21.72214970416493</v>
+        <v>25.7168811127452</v>
       </c>
     </row>
     <row r="5">
@@ -5176,10 +5176,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.51728322914684</v>
+        <v>10.67650628368406</v>
       </c>
       <c r="C5" t="n">
-        <v>18.43231314723387</v>
+        <v>29.50151851261666</v>
       </c>
       <c r="D5" t="n">
         <v>29.47697482001049</v>
@@ -5193,7 +5193,7 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
         <v>36.6290068454485</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>37.42913122440964</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.82499653339935</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>49.82369599052563</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5274,7 +5274,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
         <v>32.11100391050467</v>
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.95035713990669</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74938086956505</v>
+        <v>16.73727666095087</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1712233043468</v>
+        <v>102.0973876318003</v>
       </c>
       <c r="D21" t="n">
-        <v>5.024814260869515</v>
+        <v>5.021182998285261</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.316965639751478</v>
+        <v>5.800165436690155</v>
       </c>
       <c r="C2" t="n">
-        <v>9.634871969478198</v>
+        <v>8.034623211555896</v>
       </c>
       <c r="D2" t="n">
-        <v>21.8370141855618</v>
+        <v>29.8235317596096</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.94849145548944</v>
+        <v>17.12658870058561</v>
       </c>
       <c r="C3" t="n">
-        <v>25.06401888942107</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D3" t="n">
-        <v>31.40610905885546</v>
+        <v>41.78809103126548</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.24764676784423</v>
+        <v>29.57122259961817</v>
       </c>
       <c r="C4" t="n">
-        <v>23.67484588791183</v>
+        <v>54.79035762631024</v>
       </c>
       <c r="D4" t="n">
-        <v>27.22288209105981</v>
+        <v>33.78292025083699</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.67899386290708</v>
+        <v>24.39643045053324</v>
       </c>
       <c r="C5" t="n">
-        <v>30.43417883165113</v>
+        <v>62.3164355270663</v>
       </c>
       <c r="D5" t="n">
-        <v>30.80233422074368</v>
+        <v>31.73499453977815</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.63272854762046</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>21.37362926915731</v>
+        <v>30.43025184083414</v>
       </c>
       <c r="D6" t="n">
-        <v>37.75605320992383</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>20.84054026575129</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.01520924164921</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.60155896745857</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>46.09305471438775</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.91411459030757</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.08891517977551</v>
+        <v>18.06262381423001</v>
       </c>
       <c r="C21" t="n">
-        <v>118.0086371252021</v>
+        <v>117.8371172642624</v>
       </c>
       <c r="D21" t="n">
-        <v>6.891015306581147</v>
+        <v>6.880999548278099</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.616979526623502</v>
+        <v>5.865942532874692</v>
       </c>
       <c r="C2" t="n">
-        <v>11.54731649735098</v>
+        <v>12.05782530355933</v>
       </c>
       <c r="D2" t="n">
-        <v>30.86418432611122</v>
+        <v>27.4388665859941</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.24225500323749</v>
+        <v>16.6209886328985</v>
       </c>
       <c r="C3" t="n">
-        <v>30.53726234059704</v>
+        <v>28.78975142703771</v>
       </c>
       <c r="D3" t="n">
-        <v>39.45153149515808</v>
+        <v>51.89027490796516</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.24542123052848</v>
+        <v>22.84526907782328</v>
       </c>
       <c r="C4" t="n">
-        <v>38.88800831292041</v>
+        <v>55.23705283174254</v>
       </c>
       <c r="D4" t="n">
-        <v>31.46010518258904</v>
+        <v>40.49611105247669</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.31021657900877</v>
+        <v>21.25483779694345</v>
       </c>
       <c r="C5" t="n">
-        <v>28.17615911188346</v>
+        <v>61.38377520803183</v>
       </c>
       <c r="D5" t="n">
-        <v>27.39076094848602</v>
+        <v>29.32971266437347</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.4038014060817</v>
+        <v>11.75348351524281</v>
       </c>
       <c r="C6" t="n">
-        <v>24.15099352447154</v>
+        <v>44.84034464376883</v>
       </c>
       <c r="D6" t="n">
-        <v>30.10823859384119</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>16.88802400845363</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.075763994650552</v>
+        <v>7.058530123205803</v>
       </c>
       <c r="C21" t="n">
-        <v>67.21975794918023</v>
+        <v>67.05603617045512</v>
       </c>
       <c r="D21" t="n">
-        <v>5.306822995987914</v>
+        <v>5.293897592404352</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.861434704980958</v>
+        <v>5.043237956715865</v>
       </c>
       <c r="C2" t="n">
-        <v>8.886780218842128</v>
+        <v>9.87736365242716</v>
       </c>
       <c r="D2" t="n">
-        <v>32.33778763018569</v>
+        <v>22.44864300530757</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.83406894244906</v>
+        <v>18.99681807717578</v>
       </c>
       <c r="C3" t="n">
-        <v>40.28110830524663</v>
+        <v>40.60999378616931</v>
       </c>
       <c r="D3" t="n">
-        <v>56.70083865877454</v>
+        <v>62.39988408192727</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.11100391050467</v>
+        <v>28.67783218875358</v>
       </c>
       <c r="C4" t="n">
-        <v>63.35414285045516</v>
+        <v>65.94497504196249</v>
       </c>
       <c r="D4" t="n">
-        <v>45.51186007347363</v>
+        <v>57.90446134418112</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.03518835309942</v>
+        <v>29.08427573831176</v>
       </c>
       <c r="C5" t="n">
-        <v>55.76326960121884</v>
+        <v>86.34471058850698</v>
       </c>
       <c r="D5" t="n">
-        <v>32.96217917008666</v>
+        <v>38.2145293878071</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.54721868635975</v>
+        <v>21.41388092503143</v>
       </c>
       <c r="C6" t="n">
-        <v>36.74976181307086</v>
+        <v>75.91462297858888</v>
       </c>
       <c r="D6" t="n">
-        <v>32.6440929139107</v>
+        <v>33.65038431076368</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.73777555197486</v>
+        <v>10.36038352291659</v>
       </c>
       <c r="C7" t="n">
-        <v>27.84727363096077</v>
+        <v>46.53189593818607</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>21.27938148954961</v>
+        <v>24.11663235482289</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.5935407549086</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.304663797702396</v>
+        <v>7.279245637113043</v>
       </c>
       <c r="C21" t="n">
-        <v>77.61205285058796</v>
+        <v>76.43207918968696</v>
       </c>
       <c r="D21" t="n">
-        <v>6.391580822989597</v>
+        <v>6.369339932473912</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.759512870188536</v>
+        <v>5.163011176633976</v>
       </c>
       <c r="C2" t="n">
-        <v>5.105088062083413</v>
+        <v>14.61724156853076</v>
       </c>
       <c r="D2" t="n">
-        <v>25.68644693391354</v>
+        <v>21.23618459056275</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.0219836645877</v>
+        <v>18.29977720716055</v>
       </c>
       <c r="C3" t="n">
-        <v>36.79590395517045</v>
+        <v>39.28463438543612</v>
       </c>
       <c r="D3" t="n">
-        <v>69.41447142877074</v>
+        <v>65.88017969348221</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.1350078237631</v>
+        <v>33.14478424307656</v>
       </c>
       <c r="C4" t="n">
-        <v>85.86758120424302</v>
+        <v>86.63334441355555</v>
       </c>
       <c r="D4" t="n">
-        <v>63.2520410892135</v>
+        <v>76.16791388628454</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.98167525545136</v>
+        <v>36.86462629446773</v>
       </c>
       <c r="C5" t="n">
-        <v>90.83620633543615</v>
+        <v>105.4642471287136</v>
       </c>
       <c r="D5" t="n">
-        <v>42.41150082346221</v>
+        <v>50.020045531375</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.6440929139107</v>
+        <v>30.91327171132357</v>
       </c>
       <c r="C6" t="n">
-        <v>66.21397391292614</v>
+        <v>109.726013912849</v>
       </c>
       <c r="D6" t="n">
-        <v>35.74347041621788</v>
+        <v>38.44033135978387</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.60099382591507</v>
+        <v>18.50496247734813</v>
       </c>
       <c r="C7" t="n">
-        <v>42.27994663109313</v>
+        <v>80.96669666464294</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>30.29182541453534</v>
+        <v>44.14428552145782</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
         <v>34.28066633689012</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>22.12466626290612</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.520227116337329</v>
+        <v>7.486191446891125</v>
       </c>
       <c r="C21" t="n">
-        <v>87.42264022742145</v>
+        <v>86.09120163924793</v>
       </c>
       <c r="D21" t="n">
-        <v>7.520227116337329</v>
+        <v>7.486191446891125</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_46_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_46_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497622452601</v>
+        <v>10.84497628175887</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907156666948</v>
+        <v>37.78907176609606</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.345616249623882</v>
+        <v>0.9238245896962485</v>
       </c>
       <c r="C2" t="n">
-        <v>9.926451037639499</v>
+        <v>3.600068831473054</v>
       </c>
       <c r="D2" t="n">
-        <v>24.91872022919254</v>
+        <v>13.76999329976576</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.81381209355838</v>
+        <v>6.047565858160352</v>
       </c>
       <c r="C3" t="n">
-        <v>48.7094123462055</v>
+        <v>46.57411108946869</v>
       </c>
       <c r="D3" t="n">
-        <v>67.14663423196059</v>
+        <v>70.81837064584367</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.92331017254428</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="C4" t="n">
-        <v>91.87882239734626</v>
+        <v>161.7164270866473</v>
       </c>
       <c r="D4" t="n">
-        <v>89.55600732909829</v>
+        <v>82.65137572513048</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.09872421643498</v>
+        <v>7.878525326580655</v>
       </c>
       <c r="C5" t="n">
-        <v>133.7876683962341</v>
+        <v>206.2406489696487</v>
       </c>
       <c r="D5" t="n">
-        <v>65.16350386938205</v>
+        <v>49.08738521234053</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.57366912111219</v>
+        <v>6.31950997223672</v>
       </c>
       <c r="C6" t="n">
-        <v>138.9084644215855</v>
+        <v>142.6518684178785</v>
       </c>
       <c r="D6" t="n">
-        <v>45.00135126726531</v>
+        <v>29.46421209985528</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.42806736124739</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>118.815034158766</v>
+        <v>65.21651824541136</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20765715387736</v>
+        <v>28.62579956042849</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.26970288122739</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>75.68783925890784</v>
+        <v>30.87596529856218</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>40.93593402397924</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>37.86600895279948</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>35.12202411942965</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>83.65177663575797</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.676974062771676</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>95.0025540267995</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.636595820618137</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.753442457513809</v>
+        <v>1.018072369303942</v>
       </c>
       <c r="C2" t="n">
-        <v>7.650759859195394</v>
+        <v>2.86866679180918</v>
       </c>
       <c r="D2" t="n">
-        <v>31.13809193559609</v>
+        <v>14.69185439405352</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.65673246087889</v>
+        <v>4.560218086226434</v>
       </c>
       <c r="C3" t="n">
-        <v>43.37361357362408</v>
+        <v>28.6424892714007</v>
       </c>
       <c r="D3" t="n">
-        <v>70.09187734470103</v>
+        <v>65.65928646002668</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.41280136633594</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C4" t="n">
-        <v>105.1010004781423</v>
+        <v>139.2285141731699</v>
       </c>
       <c r="D4" t="n">
-        <v>99.02594568426302</v>
+        <v>97.67309734781091</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.36303533305563</v>
+        <v>10.13654504634832</v>
       </c>
       <c r="C5" t="n">
-        <v>150.354660905399</v>
+        <v>252.2109852210056</v>
       </c>
       <c r="D5" t="n">
-        <v>79.61973881441634</v>
+        <v>65.50711556586843</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.7850069194325</v>
+        <v>8.291841110068562</v>
       </c>
       <c r="C6" t="n">
-        <v>170.9890341532585</v>
+        <v>232.7350742641574</v>
       </c>
       <c r="D6" t="n">
-        <v>52.85042416271855</v>
+        <v>36.87051678069322</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.53083207502382</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>155.4656394537079</v>
+        <v>130.6126963206999</v>
       </c>
       <c r="D7" t="n">
-        <v>42.04040019125691</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.02903582496668</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>113.4900346109313</v>
+        <v>55.82708320199487</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.31718662392973</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>64.45468202691582</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>39.00483628972578</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.84931924182727</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>21.853703896534</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.9631198600619</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>43.93222801734051</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.85060197655788</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103.0391509423222</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.81325247069735</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.943320675060943</v>
+        <v>0.5684319207589033</v>
       </c>
       <c r="C2" t="n">
-        <v>9.004589943351744</v>
+        <v>1.327322896141688</v>
       </c>
       <c r="D2" t="n">
-        <v>32.90229256012761</v>
+        <v>10.16501572977148</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.35024725070463</v>
+        <v>4.520948178056562</v>
       </c>
       <c r="C3" t="n">
-        <v>36.78117773960675</v>
+        <v>22.64401079845268</v>
       </c>
       <c r="D3" t="n">
-        <v>75.87437132271474</v>
+        <v>64.95242811296897</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.58322455624739</v>
+        <v>11.03975293425538</v>
       </c>
       <c r="C4" t="n">
-        <v>106.1475435308694</v>
+        <v>128.6482191645021</v>
       </c>
       <c r="D4" t="n">
-        <v>107.9981379533746</v>
+        <v>106.4027979339735</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.41841411512095</v>
+        <v>10.13654504634832</v>
       </c>
       <c r="C5" t="n">
-        <v>166.6516727958961</v>
+        <v>291.2354564648164</v>
       </c>
       <c r="D5" t="n">
-        <v>91.32708018755955</v>
+        <v>72.50206795862695</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.05797383894213</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>197.5953786860513</v>
+        <v>271.9804387414237</v>
       </c>
       <c r="D6" t="n">
-        <v>62.59132488425541</v>
+        <v>37.0315234041897</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.03473068920969</v>
+        <v>4.012402867256713</v>
       </c>
       <c r="C7" t="n">
-        <v>194.1523894872577</v>
+        <v>113.7246723122463</v>
       </c>
       <c r="D7" t="n">
-        <v>45.8132566186774</v>
+        <v>32.45854259780804</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.45595720759379</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>150.7080900789279</v>
+        <v>42.97600575340412</v>
       </c>
       <c r="D8" t="n">
-        <v>39.47116644924301</v>
+        <v>35.38218726105504</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.75468624712531</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>95.07342942696533</v>
+        <v>25.07187287105504</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>54.37900533823083</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.13853390395258</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.15451960466103</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>37.98872741583033</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.006806643552572</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110.0935913488479</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.00935913488478</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.252170291271189</v>
+        <v>0.6027930904075416</v>
       </c>
       <c r="C2" t="n">
-        <v>6.266495596207391</v>
+        <v>11.40398133253095</v>
       </c>
       <c r="D2" t="n">
-        <v>27.05009449511237</v>
+        <v>10.92096146204152</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.70782439922873</v>
+        <v>3.264311116620645</v>
       </c>
       <c r="C3" t="n">
-        <v>57.62859023928777</v>
+        <v>13.57266201121215</v>
       </c>
       <c r="D3" t="n">
-        <v>81.95629835052374</v>
+        <v>58.66433406726816</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.78145547704723</v>
+        <v>10.0187353218387</v>
       </c>
       <c r="C4" t="n">
-        <v>139.2285141731699</v>
+        <v>93.70389137954106</v>
       </c>
       <c r="D4" t="n">
-        <v>103.3142196564131</v>
+        <v>113.3584804185622</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.43417883165113</v>
+        <v>12.86089492563322</v>
       </c>
       <c r="C5" t="n">
-        <v>118.055161435679</v>
+        <v>268.1889291076225</v>
       </c>
       <c r="D5" t="n">
-        <v>61.94828013797375</v>
+        <v>91.2779928023472</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.93464917663875</v>
+        <v>9.861655689159212</v>
       </c>
       <c r="C6" t="n">
-        <v>127.8795107120768</v>
+        <v>359.0045187412694</v>
       </c>
       <c r="D6" t="n">
-        <v>30.14849024971531</v>
+        <v>47.53720558733482</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.86428213710246</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>105.9394130175691</v>
+        <v>232.7792529108485</v>
       </c>
       <c r="D7" t="n">
-        <v>27.72750041104266</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>70.01333752836128</v>
+        <v>85.61821728736433</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>41.49062147687869</v>
+        <v>36.16562192904399</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.32833000604172</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>31.31775176547326</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.15451960466103</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>45.33318199130072</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.282383485924587</v>
+        <v>0.3190680038802133</v>
       </c>
       <c r="C2" t="n">
-        <v>3.290818304635308</v>
+        <v>5.707881152490955</v>
       </c>
       <c r="D2" t="n">
-        <v>19.87940926329366</v>
+        <v>8.807258654798137</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.27371198750239</v>
+        <v>2.783254741539707</v>
       </c>
       <c r="C3" t="n">
-        <v>41.85190463204153</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D3" t="n">
-        <v>85.26969685235672</v>
+        <v>54.98278017634262</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.34524070119216</v>
+        <v>8.80627690709389</v>
       </c>
       <c r="C4" t="n">
-        <v>146.4522137810179</v>
+        <v>70.33535077535424</v>
       </c>
       <c r="D4" t="n">
-        <v>116.9703302224862</v>
+        <v>116.2556178937945</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.69848994827177</v>
+        <v>14.1126232485479</v>
       </c>
       <c r="C5" t="n">
-        <v>179.0462375620121</v>
+        <v>240.7981681591365</v>
       </c>
       <c r="D5" t="n">
-        <v>78.9079717288374</v>
+        <v>104.8506548135594</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.72459622565894</v>
+        <v>11.79373517111693</v>
       </c>
       <c r="C6" t="n">
-        <v>157.7864910265474</v>
+        <v>398.9744130242698</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>56.714583126634</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.66654993792135</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>135.6431715572606</v>
+        <v>322.4295080195544</v>
       </c>
       <c r="D7" t="n">
-        <v>30.12296480940488</v>
+        <v>39.1059563032632</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>93.12858722485242</v>
+        <v>131.8487166803466</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>45.15155866601504</v>
+        <v>43.93124626963626</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>39.93749660876023</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>25.23287949455151</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.34073287329842</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.28621266575034</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>38.85168364786328</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.843943172753763</v>
+        <v>0.336739462556656</v>
       </c>
       <c r="C2" t="n">
-        <v>4.437499623195583</v>
+        <v>9.548478171504478</v>
       </c>
       <c r="D2" t="n">
-        <v>27.31320287985051</v>
+        <v>7.986517574047803</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.42878706704438</v>
+        <v>1.988039101099791</v>
       </c>
       <c r="C3" t="n">
-        <v>27.0716929446058</v>
+        <v>25.02965771977243</v>
       </c>
       <c r="D3" t="n">
-        <v>81.4605157598791</v>
+        <v>50.14767273292708</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.32644862609123</v>
+        <v>7.159886007071989</v>
       </c>
       <c r="C4" t="n">
-        <v>125.7000308086489</v>
+        <v>69.87589284976673</v>
       </c>
       <c r="D4" t="n">
-        <v>130.4988135870073</v>
+        <v>116.5619231775195</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.5398887885403</v>
+        <v>13.89173001509237</v>
       </c>
       <c r="C5" t="n">
-        <v>221.6050005411113</v>
+        <v>194.5333075965055</v>
       </c>
       <c r="D5" t="n">
-        <v>98.93562489547234</v>
+        <v>117.6133749687679</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.19882142453915</v>
+        <v>14.4503444588088</v>
       </c>
       <c r="C6" t="n">
-        <v>216.5136569468874</v>
+        <v>394.0234593517532</v>
       </c>
       <c r="D6" t="n">
-        <v>49.67054334866313</v>
+        <v>69.79637128572274</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.81112889235289</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>176.3660663294182</v>
+        <v>423.2785591906038</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>44.43586458961913</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.18348900970292</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>131.5149224609027</v>
+        <v>245.004957071834</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>39.63806355896497</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>73.99530621678632</v>
+        <v>86.75311763347362</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>38.15071578703105</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>34.04210164475815</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>9.675123625352315</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.921681167838508</v>
+        <v>0.2395464398362217</v>
       </c>
       <c r="C2" t="n">
-        <v>2.156899706230242</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="D2" t="n">
-        <v>19.07437614581128</v>
+        <v>5.877723505325654</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.79694245613693</v>
+        <v>2.709623663721197</v>
       </c>
       <c r="C3" t="n">
-        <v>24.76949457814703</v>
+        <v>32.46148784092079</v>
       </c>
       <c r="D3" t="n">
-        <v>85.36296288426017</v>
+        <v>53.70650816082176</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.98934931063608</v>
+        <v>10.3122778854085</v>
       </c>
       <c r="C4" t="n">
-        <v>118.1572631969206</v>
+        <v>105.024424157211</v>
       </c>
       <c r="D4" t="n">
-        <v>140.7983287522605</v>
+        <v>118.7443483240602</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.96342295969817</v>
+        <v>8.516661334341082</v>
       </c>
       <c r="C5" t="n">
-        <v>259.6968114658875</v>
+        <v>315.3373626040756</v>
       </c>
       <c r="D5" t="n">
-        <v>103.8443634167064</v>
+        <v>105.513334513926</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.83276839957533</v>
+        <v>5.192463607761381</v>
       </c>
       <c r="C6" t="n">
-        <v>250.7678160957628</v>
+        <v>356.0258962065846</v>
       </c>
       <c r="D6" t="n">
-        <v>48.26173539306896</v>
+        <v>59.65295400544471</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.024805734513427</v>
+        <v>3.054217107911827</v>
       </c>
       <c r="C7" t="n">
-        <v>179.7197164871253</v>
+        <v>172.2937768522025</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>91.87685890193774</v>
+        <v>63.92159302350981</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>29.06562253193106</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>25.62656032395449</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>18.8358114536793</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>13.52848336452105</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>7.989462817160544</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.46681318560274</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.739076094848601</v>
+        <v>0.1276272015520853</v>
       </c>
       <c r="C2" t="n">
-        <v>5.023603002630929</v>
+        <v>2.734167356327367</v>
       </c>
       <c r="D2" t="n">
-        <v>17.68814838741478</v>
+        <v>4.910702016642545</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.18272824617692</v>
+        <v>1.811324514335365</v>
       </c>
       <c r="C3" t="n">
-        <v>16.74370709592935</v>
+        <v>26.92933952749001</v>
       </c>
       <c r="D3" t="n">
-        <v>81.04327298557421</v>
+        <v>47.13370728088937</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.83244960440584</v>
+        <v>7.338564089244907</v>
       </c>
       <c r="C4" t="n">
-        <v>91.43212719191393</v>
+        <v>89.36456652677016</v>
       </c>
       <c r="D4" t="n">
-        <v>148.9792323717492</v>
+        <v>112.3119373658351</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.87278337573798</v>
+        <v>8.811185645615124</v>
       </c>
       <c r="C5" t="n">
-        <v>242.7371198750239</v>
+        <v>233.3368856068607</v>
       </c>
       <c r="D5" t="n">
-        <v>124.7065021319511</v>
+        <v>109.8330244126119</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.9698942830004</v>
+        <v>4.789947049020189</v>
       </c>
       <c r="C6" t="n">
-        <v>321.6107304342127</v>
+        <v>346.9290219790337</v>
       </c>
       <c r="D6" t="n">
-        <v>64.48315271033901</v>
+        <v>62.51082157250717</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.46881773874025</v>
+        <v>2.215804568485051</v>
       </c>
       <c r="C7" t="n">
-        <v>257.0333299442659</v>
+        <v>221.7601166783822</v>
       </c>
       <c r="D7" t="n">
-        <v>37.72856427420492</v>
+        <v>31.91956310817654</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>0.9179341034707675</v>
       </c>
       <c r="C8" t="n">
-        <v>147.9542877685155</v>
+        <v>77.85750168529329</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>25.36836067773758</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>59.68436993198057</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>12.26104707833841</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>7.804894248762142</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.458296251434013</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.963495408493621</v>
+        <v>0.09522952731194061</v>
       </c>
       <c r="C2" t="n">
-        <v>2.919717672430014</v>
+        <v>9.688868093211772</v>
       </c>
       <c r="D2" t="n">
-        <v>14.30210055546753</v>
+        <v>6.757369448330795</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.92470852640926</v>
+        <v>1.08973995171396</v>
       </c>
       <c r="C3" t="n">
-        <v>18.28014225307561</v>
+        <v>17.79417713947344</v>
       </c>
       <c r="D3" t="n">
-        <v>77.59242980514665</v>
+        <v>40.63453747877548</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.22059980048183</v>
+        <v>5.385867905498002</v>
       </c>
       <c r="C4" t="n">
-        <v>73.76852249710534</v>
+        <v>77.46971134211582</v>
       </c>
       <c r="D4" t="n">
-        <v>153.5738116276243</v>
+        <v>110.6655464658132</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.70789081915352</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C5" t="n">
-        <v>222.1940491636594</v>
+        <v>200.0310947402877</v>
       </c>
       <c r="D5" t="n">
-        <v>140.3899217072939</v>
+        <v>123.7983855055228</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.249152599363</v>
+        <v>8.010079518949729</v>
       </c>
       <c r="C6" t="n">
-        <v>357.3139491945564</v>
+        <v>360.1718167616189</v>
       </c>
       <c r="D6" t="n">
-        <v>75.71336469921827</v>
+        <v>79.09450379264429</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.61233283000952</v>
+        <v>3.712969817461437</v>
       </c>
       <c r="C7" t="n">
-        <v>324.4656527581623</v>
+        <v>359.4394329742507</v>
       </c>
       <c r="D7" t="n">
-        <v>41.98051358129786</v>
+        <v>41.14210104187108</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>192.3489189545563</v>
+        <v>177.4950761893021</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>28.12216298814988</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>66.22968187619405</v>
+        <v>59.12968247908112</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>21.74374815365835</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>23.34596040698915</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>14.74879576089983</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>12.36707583039707</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.835287369864788</v>
+        <v>0.1462804079327747</v>
       </c>
       <c r="C2" t="n">
-        <v>17.44762019987432</v>
+        <v>20.16607959293373</v>
       </c>
       <c r="D2" t="n">
-        <v>17.14327841155781</v>
+        <v>10.71773968726243</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.01382658331747</v>
+        <v>0.7117670855789375</v>
       </c>
       <c r="C3" t="n">
-        <v>15.07964473723101</v>
+        <v>27.70001147532376</v>
       </c>
       <c r="D3" t="n">
-        <v>72.06519023023712</v>
+        <v>36.96770980341365</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.70710469343173</v>
+        <v>3.75223972563131</v>
       </c>
       <c r="C4" t="n">
-        <v>61.64393834965723</v>
+        <v>61.1717177039145</v>
       </c>
       <c r="D4" t="n">
-        <v>155.3733551695087</v>
+        <v>106.4793742549048</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.87969666739671</v>
+        <v>9.252972112526189</v>
       </c>
       <c r="C5" t="n">
-        <v>186.7038696551372</v>
+        <v>172.8121396400448</v>
       </c>
       <c r="D5" t="n">
-        <v>154.1098458741431</v>
+        <v>133.6894936258094</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.2252718592916</v>
+        <v>10.34467555964864</v>
       </c>
       <c r="C6" t="n">
-        <v>357.0321876034376</v>
+        <v>339.3617106746993</v>
       </c>
       <c r="D6" t="n">
-        <v>94.02786812194252</v>
+        <v>95.11466283054375</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.5478405811655</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C7" t="n">
-        <v>397.4075436882918</v>
+        <v>435.3157677923739</v>
       </c>
       <c r="D7" t="n">
-        <v>49.82565948593412</v>
+        <v>51.92169083450106</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.42692138262712</v>
+        <v>2.503456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>280.637489997472</v>
+        <v>310.5120726377024</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.8874999246391163</v>
       </c>
       <c r="C9" t="n">
-        <v>123.6953019965768</v>
+        <v>128.3546766009322</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>23.2968730217768</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>46.26486056263094</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>20.78359889890498</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>6.808420328951629</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.677046063031804</v>
+        <v>1.931097734253476</v>
       </c>
       <c r="C2" t="n">
-        <v>6.48542533425443</v>
+        <v>24.47889725768997</v>
       </c>
       <c r="D2" t="n">
-        <v>6.401976779393451</v>
+        <v>14.4356182432451</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.072469403665017</v>
+        <v>0.08835729338221293</v>
       </c>
       <c r="C2" t="n">
-        <v>10.32896759638069</v>
+        <v>14.93140083388974</v>
       </c>
       <c r="D2" t="n">
-        <v>12.75486617357456</v>
+        <v>10.93077893908399</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.57266201121215</v>
+        <v>0.5939573610693203</v>
       </c>
       <c r="C3" t="n">
-        <v>31.69081589308704</v>
+        <v>50.64836406209295</v>
       </c>
       <c r="D3" t="n">
-        <v>78.56926877087224</v>
+        <v>36.59464567579985</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.79790850830795</v>
+        <v>2.641883072128167</v>
       </c>
       <c r="C4" t="n">
-        <v>94.21440018574941</v>
+        <v>63.78807533573226</v>
       </c>
       <c r="D4" t="n">
-        <v>156.4581863827015</v>
+        <v>101.7444050773224</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.6122760767473</v>
+        <v>7.878525326580655</v>
       </c>
       <c r="C5" t="n">
-        <v>291.4318060056657</v>
+        <v>145.298660228528</v>
       </c>
       <c r="D5" t="n">
-        <v>139.6045235438964</v>
+        <v>137.8864650614645</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.10695374650067</v>
+        <v>11.10945702125691</v>
       </c>
       <c r="C6" t="n">
-        <v>324.7101079365199</v>
+        <v>314.4056840327453</v>
       </c>
       <c r="D6" t="n">
-        <v>74.02279515250527</v>
+        <v>110.5310470303314</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.910702016642545</v>
+        <v>8.503898614185871</v>
       </c>
       <c r="C7" t="n">
-        <v>197.3263798150876</v>
+        <v>457.4139268672653</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>62.28207435741764</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>91.12582190818894</v>
+        <v>420.5807164993336</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>35.27812200440487</v>
+        <v>227.3109181981937</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>24.96093538047515</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>84.55792976677779</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.208973392284329</v>
+        <v>2.4160811001514</v>
       </c>
       <c r="C2" t="n">
-        <v>8.173049637854696</v>
+        <v>15.87289688226243</v>
       </c>
       <c r="D2" t="n">
-        <v>17.45449243380404</v>
+        <v>28.86534600026472</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.940195505498956</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="C3" t="n">
-        <v>16.60135367881356</v>
+        <v>48.33143948007048</v>
       </c>
       <c r="D3" t="n">
-        <v>8.511752595819846</v>
+        <v>12.84616871006951</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.63749841742144</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>45.69544689416779</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39898769373022</v>
+        <v>11.67614121176464</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14764145541113</v>
+        <v>59.9375248870585</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576351493380025</v>
+        <v>0.7784094141176429</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.432590884674349</v>
+        <v>1.575705065316131</v>
       </c>
       <c r="C2" t="n">
-        <v>5.667629496616836</v>
+        <v>12.64883742151591</v>
       </c>
       <c r="D2" t="n">
-        <v>15.42816517223863</v>
+        <v>22.36421270274234</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.85446466005999</v>
+        <v>6.371542600561799</v>
       </c>
       <c r="C3" t="n">
-        <v>26.15375884113503</v>
+        <v>57.33406592801373</v>
       </c>
       <c r="D3" t="n">
-        <v>21.11248437982766</v>
+        <v>35.01894061048372</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.65236350170539</v>
+        <v>4.058545009356314</v>
       </c>
       <c r="C4" t="n">
-        <v>25.83174559414208</v>
+        <v>77.82706750646165</v>
       </c>
       <c r="D4" t="n">
-        <v>19.52696183746906</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.3497485290859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.06307819944583</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.18020927588745</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44241494232473</v>
+        <v>13.6194732875276</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15242020454849</v>
+        <v>73.70538485014937</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251034724699943</v>
+        <v>1.602290975003247</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.058945919983814</v>
+        <v>1.174170254279185</v>
       </c>
       <c r="C2" t="n">
-        <v>8.883834975729387</v>
+        <v>7.6487963637869</v>
       </c>
       <c r="D2" t="n">
-        <v>25.77185898418302</v>
+        <v>19.00074506799277</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.87624303600267</v>
+        <v>5.861033794353458</v>
       </c>
       <c r="C3" t="n">
-        <v>23.66502841086936</v>
+        <v>52.3713312830461</v>
       </c>
       <c r="D3" t="n">
-        <v>28.55413197801848</v>
+        <v>44.78242152921825</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.62754207165874</v>
+        <v>8.819039627249097</v>
       </c>
       <c r="C4" t="n">
-        <v>49.17476075801849</v>
+        <v>117.2383473457456</v>
       </c>
       <c r="D4" t="n">
-        <v>25.7168811127452</v>
+        <v>33.6425303291297</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.67650628368406</v>
+        <v>4.442408361716818</v>
       </c>
       <c r="C5" t="n">
-        <v>29.50151851261666</v>
+        <v>85.48568134729102</v>
       </c>
       <c r="D5" t="n">
-        <v>29.47697482001049</v>
+        <v>27.75891633757857</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.08056973167303</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.09922293805371</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.78283813537898</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.60177995163684</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>40.84561323518855</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73727666095087</v>
+        <v>14.81491973839571</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0973876318003</v>
+        <v>87.24341623721919</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021182998285261</v>
+        <v>2.469153289732619</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.800165436690155</v>
+        <v>1.091703447122453</v>
       </c>
       <c r="C2" t="n">
-        <v>8.034623211555896</v>
+        <v>6.298893270447535</v>
       </c>
       <c r="D2" t="n">
-        <v>29.8235317596096</v>
+        <v>26.24702487303848</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.12658870058561</v>
+        <v>4.849833658979243</v>
       </c>
       <c r="C3" t="n">
-        <v>29.89421759431538</v>
+        <v>39.05392367493812</v>
       </c>
       <c r="D3" t="n">
-        <v>41.78809103126548</v>
+        <v>49.25919106058371</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.57122259961817</v>
+        <v>10.159125243546</v>
       </c>
       <c r="C4" t="n">
-        <v>54.79035762631024</v>
+        <v>125.1512338419749</v>
       </c>
       <c r="D4" t="n">
-        <v>33.78292025083699</v>
+        <v>47.38797993628929</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.39643045053324</v>
+        <v>8.933904108645976</v>
       </c>
       <c r="C5" t="n">
-        <v>62.3164355270663</v>
+        <v>157.5950502242192</v>
       </c>
       <c r="D5" t="n">
-        <v>31.73499453977815</v>
+        <v>33.64940256305943</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.2641722479004</v>
+        <v>5.353470231257858</v>
       </c>
       <c r="C6" t="n">
-        <v>30.43025184083414</v>
+        <v>76.35739119320418</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>33.93214590188251</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>25.53525778745954</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>43.41779222031519</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>42.74234979979338</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06262381423001</v>
+        <v>16.03292346839816</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8371172642624</v>
+        <v>100.4167311968095</v>
       </c>
       <c r="D21" t="n">
-        <v>6.880999548278099</v>
+        <v>3.375352309136455</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.865942532874692</v>
+        <v>1.474585051778709</v>
       </c>
       <c r="C2" t="n">
-        <v>12.05782530355933</v>
+        <v>14.69087264634927</v>
       </c>
       <c r="D2" t="n">
-        <v>27.4388665859941</v>
+        <v>30.28888017142259</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.6209886328985</v>
+        <v>4.231332605303753</v>
       </c>
       <c r="C3" t="n">
-        <v>28.78975142703771</v>
+        <v>31.09685853201772</v>
       </c>
       <c r="D3" t="n">
-        <v>51.89027490796516</v>
+        <v>57.67276888597888</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.84526907782328</v>
+        <v>9.737955478424112</v>
       </c>
       <c r="C4" t="n">
-        <v>55.23705283174254</v>
+        <v>109.5551898123101</v>
       </c>
       <c r="D4" t="n">
-        <v>40.49611105247669</v>
+        <v>59.88268296823845</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.25483779694345</v>
+        <v>11.85460352878024</v>
       </c>
       <c r="C5" t="n">
-        <v>61.38377520803183</v>
+        <v>194.9750940634166</v>
       </c>
       <c r="D5" t="n">
-        <v>29.32971266437347</v>
+        <v>41.67519004527711</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.75348351524281</v>
+        <v>8.533351045313278</v>
       </c>
       <c r="C6" t="n">
-        <v>44.84034464376883</v>
+        <v>161.2078817758475</v>
       </c>
       <c r="D6" t="n">
-        <v>30.79251674370121</v>
+        <v>36.91076843656734</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>6.467753875577986</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>61.6832082578271</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.06405994715006</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.71718421238145</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>43.13308538608361</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.058530123205803</v>
+        <v>17.26503711941568</v>
       </c>
       <c r="C21" t="n">
-        <v>67.05603617045512</v>
+        <v>113.0859931321727</v>
       </c>
       <c r="D21" t="n">
-        <v>5.293897592404352</v>
+        <v>4.316259279853921</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.043237956715865</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C2" t="n">
-        <v>9.87736365242716</v>
+        <v>11.42361628661589</v>
       </c>
       <c r="D2" t="n">
-        <v>22.44864300530757</v>
+        <v>24.74396913783661</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.99681807717578</v>
+        <v>4.520948178056562</v>
       </c>
       <c r="C3" t="n">
-        <v>40.60999378616931</v>
+        <v>43.72704274715294</v>
       </c>
       <c r="D3" t="n">
-        <v>62.39988408192727</v>
+        <v>65.88999717052468</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.67783218875358</v>
+        <v>8.80627690709389</v>
       </c>
       <c r="C4" t="n">
-        <v>65.94497504196249</v>
+        <v>92.98917905084939</v>
       </c>
       <c r="D4" t="n">
-        <v>57.90446134418112</v>
+        <v>71.31808022730529</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.08427573831176</v>
+        <v>13.10633185169492</v>
       </c>
       <c r="C5" t="n">
-        <v>86.34471058850698</v>
+        <v>197.9939682539755</v>
       </c>
       <c r="D5" t="n">
-        <v>38.2145293878071</v>
+        <v>51.68901662859458</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.41388092503143</v>
+        <v>11.67298020349458</v>
       </c>
       <c r="C6" t="n">
-        <v>75.91462297858888</v>
+        <v>228.186637150382</v>
       </c>
       <c r="D6" t="n">
-        <v>33.65038431076368</v>
+        <v>40.57366912111219</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.36038352291659</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="C7" t="n">
-        <v>46.53189593818607</v>
+        <v>136.122264436933</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>24.11663235482289</v>
+        <v>50.06913291658733</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>42.99073196896783</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.26022956155019</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>29.80684204863741</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>28.30869505195678</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.279245637113043</v>
+        <v>17.62235907988271</v>
       </c>
       <c r="C21" t="n">
-        <v>76.43207918968696</v>
+        <v>125.1187494671672</v>
       </c>
       <c r="D21" t="n">
-        <v>6.369339932473912</v>
+        <v>5.286707723964812</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.163011176633976</v>
+        <v>1.712167996206437</v>
       </c>
       <c r="C2" t="n">
-        <v>14.61724156853076</v>
+        <v>7.493680226515903</v>
       </c>
       <c r="D2" t="n">
-        <v>21.23618459056275</v>
+        <v>20.10324773986193</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.29977720716055</v>
+        <v>5.85121631731099</v>
       </c>
       <c r="C3" t="n">
-        <v>39.28463438543612</v>
+        <v>63.93631923907353</v>
       </c>
       <c r="D3" t="n">
-        <v>65.88017969348221</v>
+        <v>69.87589284976673</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.14478424307656</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C4" t="n">
-        <v>86.63334441355555</v>
+        <v>152.3996413733451</v>
       </c>
       <c r="D4" t="n">
-        <v>76.16791388628454</v>
+        <v>65.54933071715104</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.86462629446773</v>
+        <v>6.553165925847461</v>
       </c>
       <c r="C5" t="n">
-        <v>105.4642471287136</v>
+        <v>136.3402124272758</v>
       </c>
       <c r="D5" t="n">
-        <v>50.020045531375</v>
+        <v>38.63177216211199</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.91327171132357</v>
+        <v>4.991205328390785</v>
       </c>
       <c r="C6" t="n">
-        <v>109.726013912849</v>
+        <v>89.64043763166353</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>25.39879485656924</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.50496247734813</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>80.96669666464294</v>
+        <v>35.2133266559246</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>26.40999499194344</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>44.14428552145782</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>27.5124976638126</v>
+        <v>25.4046853427947</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>24.71549845441346</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>33.49428642578843</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>29.75873641112932</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>95.49459919208724</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.486191446891125</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>86.09120163924793</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.486191446891125</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
